--- a/tools/_out/groupB_20261021/out/fs/DesignTable_FS2404_SW2.xlsx
+++ b/tools/_out/groupB_20261021/out/fs/DesignTable_FS2404_SW2.xlsx
@@ -905,7 +905,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p3 FS2404-04-02 (ORFS-p003-t04) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p3 FS2404-04-02 (ORFS-p003-t04) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p3 FS2404-04-04 (ORFS-p003-t04) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p3 FS2404-04-04 (ORFS-p003-t04) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p3 FS2404-04-06 (ORFS-p003-t04) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p3 FS2404-04-06 (ORFS-p003-t04) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p3 FS2404-06-04 (ORFS-p003-t04) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p3 FS2404-06-04 (ORFS-p003-t04) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p3 FS2404-06-06 (ORFS-p003-t04) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p3 FS2404-06-06 (ORFS-p003-t04) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p3 FS2404-06-08 (ORFS-p003-t04) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p3 FS2404-06-08 (ORFS-p003-t04) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p3 FS2404-10-08 (ORFS-p003-t04) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-10-10 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p3 FS2404-10-08 (ORFS-p003-t04) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-10-10 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p3 FS2404-10-12 (ORFS-p003-t04) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-10-10 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p3 FS2404-10-12 (ORFS-p003-t04) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-10-10 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p3 FS2404-12-08 (ORFS-p003-t04) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-12-12 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p3 FS2404-12-08 (ORFS-p003-t04) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-12-12 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p3 FS2404-12-12 (ORFS-p003-t04) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-12-12 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p3 FS2404-12-12 (ORFS-p003-t04) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-12-12 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p3 FS2404-12-16 (ORFS-p003-t04) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-12-12 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p3 FS2404-12-16 (ORFS-p003-t04) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-12-12 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p4 FS2404-16-12 (ORFS-p004-t01) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-16-16 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p4 FS2404-16-12 (ORFS-p004-t01) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-16-16 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p4 FS2404-16-16 (ORFS-p004-t01) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-16-16 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p4 FS2404-16-16 (ORFS-p004-t01) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-16-16 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p4 FS2404-16-20 (ORFS-p004-t01) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-16-16 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p4 FS2404-16-20 (ORFS-p004-t01) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-16-16 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p4 FS2404-20-16 (ORFS-p004-t01) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-20-20 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p4 FS2404-20-16 (ORFS-p004-t01) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-20-20 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p4 FS2404-20-20 (ORFS-p004-t01) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-20-20 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>Air-Way FF2404 (s10, double-pass 2026-10-15, parts.air-way.com/api/series/10, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p4 FS2404-20-20 (ORFS-p004-t01) | MODEL: L face -&gt; pipe tip, hex S1, bores D2 (pipe side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length (ASSUMPTION, as 2404); hex between the two ends; bore step at the hex mid-plane (ASSUMPTION, as 2403); hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-20-20 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
